--- a/data/trans_orig/P57_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44909</t>
+          <t>43562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74463</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>27849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52431</t>
+          <t>53312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78640</t>
+          <t>78683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118072</t>
+          <t>116953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352677</t>
+          <t>353015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382231</t>
+          <t>383578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292635</t>
+          <t>291754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316270</t>
+          <t>317217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>654134</t>
+          <t>655253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693566</t>
+          <t>693523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32663</t>
+          <t>34390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59371</t>
+          <t>60629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>41281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69299</t>
+          <t>70041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82145</t>
+          <t>83288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120623</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315410</t>
+          <t>314152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342118</t>
+          <t>340391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299698</t>
+          <t>298956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328558</t>
+          <t>327716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>623155</t>
+          <t>621477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>661633</t>
+          <t>660490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97272</t>
+          <t>97669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134860</t>
+          <t>135287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37003</t>
+          <t>37139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>62244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144266</t>
+          <t>144598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192005</t>
+          <t>192091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384119</t>
+          <t>383692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421707</t>
+          <t>421310</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101162</t>
+          <t>102334</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127575</t>
+          <t>127439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>491553</t>
+          <t>491467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>539292</t>
+          <t>538960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190804</t>
+          <t>190012</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245739</t>
+          <t>241907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148945</t>
+          <t>147819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195505</t>
+          <t>194675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>351781</t>
+          <t>351264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>419540</t>
+          <t>421983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>899737</t>
+          <t>903569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>954672</t>
+          <t>955464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>629345</t>
+          <t>630175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>675905</t>
+          <t>677031</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1550786</t>
+          <t>1548343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1618545</t>
+          <t>1619062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148955</t>
+          <t>147742</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193784</t>
+          <t>192970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208373</t>
+          <t>209161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259591</t>
+          <t>257334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>366763</t>
+          <t>370365</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>435389</t>
+          <t>439482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424799</t>
+          <t>425613</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469628</t>
+          <t>470841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476442</t>
+          <t>478699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>527660</t>
+          <t>526872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>919228</t>
+          <t>915135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>987854</t>
+          <t>984252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29330</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>249975</t>
+          <t>249904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>312954</t>
+          <t>309138</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>268869</t>
+          <t>267399</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>328794</t>
+          <t>334925</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257815</t>
+          <t>259102</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276161</t>
+          <t>275907</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>762679</t>
+          <t>766495</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>825658</t>
+          <t>825729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1033984</t>
+          <t>1027853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1093909</t>
+          <t>1095379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>580897</t>
+          <t>578607</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>668331</t>
+          <t>671036</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>775630</t>
+          <t>781455</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>879517</t>
+          <t>881610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1381153</t>
+          <t>1385966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1521034</t>
+          <t>1515342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2703774</t>
+          <t>2701069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2791208</t>
+          <t>2793498</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2635640</t>
+          <t>2633547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2739527</t>
+          <t>2733702</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5366228</t>
+          <t>5371920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5506109</t>
+          <t>5501296</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44826</t>
+          <t>44703</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77268</t>
+          <t>75657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>28538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47588</t>
+          <t>48483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78595</t>
+          <t>79124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114784</t>
+          <t>113597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427944</t>
+          <t>429555</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460386</t>
+          <t>460509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>398826</t>
+          <t>397931</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418003</t>
+          <t>417876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>836843</t>
+          <t>838030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>873032</t>
+          <t>872503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59120</t>
+          <t>57742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>37258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59491</t>
+          <t>59273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>77561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109769</t>
+          <t>112611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392472</t>
+          <t>393850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417245</t>
+          <t>418157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321491</t>
+          <t>321709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>342964</t>
+          <t>343724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722805</t>
+          <t>719963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755259</t>
+          <t>755013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106492</t>
+          <t>106528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>41101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40358</t>
+          <t>43200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140305</t>
+          <t>140656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561772</t>
+          <t>561736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645381</t>
+          <t>644407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127074</t>
+          <t>125810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141921</t>
+          <t>141970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694870</t>
+          <t>694519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>794817</t>
+          <t>791975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133842</t>
+          <t>130464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175930</t>
+          <t>175725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46796</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123774</t>
+          <t>124199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168745</t>
+          <t>176795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284634</t>
+          <t>284256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853179</t>
+          <t>853384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>895267</t>
+          <t>898645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>850393</t>
+          <t>849968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>927371</t>
+          <t>922314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1718642</t>
+          <t>1719020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1834531</t>
+          <t>1826481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78237</t>
+          <t>76796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112389</t>
+          <t>108511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137750</t>
+          <t>137746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218698</t>
+          <t>216759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227482</t>
+          <t>228893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>314446</t>
+          <t>314971</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360192</t>
+          <t>364070</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>394344</t>
+          <t>395785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>618509</t>
+          <t>620448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>699457</t>
+          <t>699461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>995342</t>
+          <t>994817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1082306</t>
+          <t>1080895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20245</t>
+          <t>19999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>150713</t>
+          <t>148336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188085</t>
+          <t>188545</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158874</t>
+          <t>157777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201377</t>
+          <t>201585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220262</t>
+          <t>220508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235567</t>
+          <t>235465</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>564353</t>
+          <t>563893</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601725</t>
+          <t>604102</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>791568</t>
+          <t>791360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>834071</t>
+          <t>835168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,11%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>322986</t>
+          <t>313434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>473933</t>
+          <t>470225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>467667</t>
+          <t>461408</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>624734</t>
+          <t>618933</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>853300</t>
+          <t>860520</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1073062</t>
+          <t>1073061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2893333</t>
+          <t>2897041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3044280</t>
+          <t>3053832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2933384</t>
+          <t>2939185</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3090451</t>
+          <t>3096710</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5852322</t>
+          <t>5852323</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6072084</t>
+          <t>6064864</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43562</t>
+          <t>44693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>72962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27849</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53312</t>
+          <t>53040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78683</t>
+          <t>79703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116953</t>
+          <t>118100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353015</t>
+          <t>354178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383578</t>
+          <t>382447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291754</t>
+          <t>292026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>317217</t>
+          <t>317133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>655253</t>
+          <t>654106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693523</t>
+          <t>692503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34390</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60629</t>
+          <t>60966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41281</t>
+          <t>40404</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70041</t>
+          <t>69356</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83288</t>
+          <t>82209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122301</t>
+          <t>119236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>314152</t>
+          <t>313815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>340391</t>
+          <t>340372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>298956</t>
+          <t>299641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327716</t>
+          <t>328593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621477</t>
+          <t>624542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>660490</t>
+          <t>661569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,95%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97669</t>
+          <t>96407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135287</t>
+          <t>136473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>36971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62244</t>
+          <t>64088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144598</t>
+          <t>142387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192091</t>
+          <t>188750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383692</t>
+          <t>382506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421310</t>
+          <t>422572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102334</t>
+          <t>100490</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>127607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>491467</t>
+          <t>494808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>538960</t>
+          <t>541171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190012</t>
+          <t>189400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>241907</t>
+          <t>242555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147819</t>
+          <t>148887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194675</t>
+          <t>197706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>351264</t>
+          <t>351767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>421983</t>
+          <t>420466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903569</t>
+          <t>902921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>955464</t>
+          <t>956076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630175</t>
+          <t>627144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>677031</t>
+          <t>675963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1548343</t>
+          <t>1549860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1619062</t>
+          <t>1618559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147742</t>
+          <t>147770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192970</t>
+          <t>191390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>209161</t>
+          <t>207516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>257334</t>
+          <t>260962</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>370365</t>
+          <t>367024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>439482</t>
+          <t>434874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425613</t>
+          <t>427193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470841</t>
+          <t>470813</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>478699</t>
+          <t>475071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>526872</t>
+          <t>528517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>915135</t>
+          <t>919743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>984252</t>
+          <t>987593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>28443</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>249904</t>
+          <t>251712</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>309138</t>
+          <t>313822</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>267399</t>
+          <t>266872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>334925</t>
+          <t>332766</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259102</t>
+          <t>258702</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275907</t>
+          <t>276261</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>766495</t>
+          <t>761811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>825729</t>
+          <t>823921</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1027853</t>
+          <t>1030012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1095379</t>
+          <t>1095906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>578607</t>
+          <t>578718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>671036</t>
+          <t>673678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>781455</t>
+          <t>774897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>881610</t>
+          <t>876973</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1385966</t>
+          <t>1379794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1515342</t>
+          <t>1521472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2701069</t>
+          <t>2698427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2793498</t>
+          <t>2793387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2633547</t>
+          <t>2638184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2733702</t>
+          <t>2740260</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5371920</t>
+          <t>5365790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5501296</t>
+          <t>5507468</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>57132</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>48776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75657</t>
+          <t>81388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>44437</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48483</t>
+          <t>57276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>94470</t>
+          <t>107421</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79124</t>
+          <t>89909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113597</t>
+          <t>129856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -3474,32 +3474,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>448080</t>
+          <t>487634</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429555</t>
+          <t>469230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460509</t>
+          <t>501842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>409076</t>
+          <t>442842</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>397931</t>
+          <t>430003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417876</t>
+          <t>453141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>857157</t>
+          <t>930476</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>838030</t>
+          <t>908041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>872503</t>
+          <t>947988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446414</t>
+          <t>487279</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446414</t>
+          <t>487279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446414</t>
+          <t>487279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951627</t>
+          <t>1037897</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951627</t>
+          <t>1037897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951627</t>
+          <t>1037897</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>34898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57742</t>
+          <t>60811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37258</t>
+          <t>42894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59273</t>
+          <t>66272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92341</t>
+          <t>99870</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77561</t>
+          <t>84263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112611</t>
+          <t>117711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>406897</t>
+          <t>435911</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393850</t>
+          <t>421734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418157</t>
+          <t>447647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>333336</t>
+          <t>368234</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321709</t>
+          <t>355197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>343724</t>
+          <t>378575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,27 +3887,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>740233</t>
+          <t>804144</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>719963</t>
+          <t>786303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755013</t>
+          <t>819751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451592</t>
+          <t>482545</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451592</t>
+          <t>482545</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451592</t>
+          <t>482545</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380982</t>
+          <t>421469</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380982</t>
+          <t>421469</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380982</t>
+          <t>421469</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832574</t>
+          <t>904014</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832574</t>
+          <t>904014</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832574</t>
+          <t>904014</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63447</t>
+          <t>67837</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>54716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106528</t>
+          <t>83715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>34480</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24941</t>
+          <t>26663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41101</t>
+          <t>44096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>95293</t>
+          <t>102317</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43200</t>
+          <t>86762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140656</t>
+          <t>120598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>604817</t>
+          <t>403775</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561736</t>
+          <t>387897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644407</t>
+          <t>416896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>135065</t>
+          <t>153017</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125810</t>
+          <t>143401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141970</t>
+          <t>160834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>739882</t>
+          <t>556792</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694519</t>
+          <t>538511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>791975</t>
+          <t>572347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>153726</t>
+          <t>164057</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130464</t>
+          <t>142627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175725</t>
+          <t>187864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92399</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>91722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124199</t>
+          <t>122141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>269701</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176795</t>
+          <t>242779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284256</t>
+          <t>299042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>875383</t>
+          <t>961464</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853384</t>
+          <t>937657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>898645</t>
+          <t>982894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>881768</t>
+          <t>751003</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>849968</t>
+          <t>734505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>922314</t>
+          <t>764924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1757152</t>
+          <t>1712466</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1719020</t>
+          <t>1683125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1826481</t>
+          <t>1739388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1029109</t>
+          <t>1125521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1029109</t>
+          <t>1125521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1029109</t>
+          <t>1125521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>974167</t>
+          <t>856646</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>974167</t>
+          <t>856646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>974167</t>
+          <t>856646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2003276</t>
+          <t>1982167</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2003276</t>
+          <t>1982167</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2003276</t>
+          <t>1982167</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,102 +4733,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92709</t>
+          <t>108700</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76796</t>
+          <t>91269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108511</t>
+          <t>127045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>210884</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>193329</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>232056</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>25,52%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>23,39%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>319583</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>290612</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>346624</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>22,96%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>187366</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>137746</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>216759</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>16,45%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>25,89%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>280075</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>228893</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>314971</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>21,38%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -4846,102 +4846,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>379872</t>
+          <t>456691</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364070</t>
+          <t>438346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395785</t>
+          <t>474122</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>77,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>615617</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>594445</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>633172</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>76,61%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1072308</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1045267</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1101279</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>77,04%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>649841</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>620448</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>699461</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>77,62%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>74,11%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>83,55%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1029713</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>994817</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1080895</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>78,62%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472581</t>
+          <t>565391</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472581</t>
+          <t>565391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472581</t>
+          <t>565391</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837207</t>
+          <t>826501</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837207</t>
+          <t>826501</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837207</t>
+          <t>826501</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1309788</t>
+          <t>1391891</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1309788</t>
+          <t>1391891</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1309788</t>
+          <t>1391891</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19999</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>168823</t>
+          <t>183920</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>148336</t>
+          <t>164217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188545</t>
+          <t>204713</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>179406</t>
+          <t>196351</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157777</t>
+          <t>175012</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201585</t>
+          <t>218862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>229924</t>
+          <t>224797</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220508</t>
+          <t>213867</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235465</t>
+          <t>230686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>583615</t>
+          <t>651977</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>563893</t>
+          <t>631184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>604102</t>
+          <t>671680</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>813539</t>
+          <t>876774</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>791360</t>
+          <t>854263</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>835168</t>
+          <t>898113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>752438</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>752438</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>752438</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>992945</t>
+          <t>1073125</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>992945</t>
+          <t>1073125</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>992945</t>
+          <t>1073125</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>422291</t>
+          <t>462644</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>313434</t>
+          <t>424870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>470225</t>
+          <t>505602</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>565417</t>
+          <t>632599</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>461408</t>
+          <t>596176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>618933</t>
+          <t>670618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>987709</t>
+          <t>1095243</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>860520</t>
+          <t>1040312</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1073061</t>
+          <t>1156487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2944975</t>
+          <t>2970270</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2897041</t>
+          <t>2927312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3053832</t>
+          <t>3008044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2992701</t>
+          <t>2982689</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2939185</t>
+          <t>2944670</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3096710</t>
+          <t>3019112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5937675</t>
+          <t>5952960</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5852323</t>
+          <t>5891716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6064864</t>
+          <t>6007891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3367266</t>
+          <t>3432914</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3367266</t>
+          <t>3432914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3367266</t>
+          <t>3432914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3558118</t>
+          <t>3615288</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3558118</t>
+          <t>3615288</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3558118</t>
+          <t>3615288</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6925384</t>
+          <t>7048203</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6925384</t>
+          <t>7048203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6925384</t>
+          <t>7048203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
